--- a/项目文档/优化后excel配置表/立即遥控指令配置表_优化后.xlsx
+++ b/项目文档/优化后excel配置表/立即遥控指令配置表_优化后.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Codex Workspace\04_projects\项目文档\优化后excel配置表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DB87C72-4BFC-4B30-9832-8ABC3E6D40A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CA5C7CE-331F-4A2A-A6E1-513DC1947171}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-7560" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="立即遥控指令" sheetId="1" r:id="rId1"/>
@@ -1320,9 +1320,6 @@
     <t>单帧数据</t>
   </si>
   <si>
-    <t>源包序列计数</t>
-  </si>
-  <si>
     <t>0</t>
   </si>
   <si>
@@ -1546,6 +1543,10 @@
   </si>
   <si>
     <t>0514</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>源包序列计数</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -2033,13 +2034,13 @@
         <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="L1" s="1" t="s">
-        <v>462</v>
-      </c>
       <c r="M1" s="1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>10</v>
@@ -2362,10 +2363,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>13</v>
@@ -2392,18 +2393,18 @@
       <c r="L11" s="7"/>
       <c r="M11" s="7"/>
       <c r="N11" s="10" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="12" spans="1:14">
       <c r="A12" s="6">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>13</v>
@@ -2430,18 +2431,18 @@
       <c r="L12" s="7"/>
       <c r="M12" s="7"/>
       <c r="N12" s="11" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="13" spans="1:14">
       <c r="A13" s="6">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>13</v>
@@ -2468,12 +2469,12 @@
       <c r="L13" s="7"/>
       <c r="M13" s="7"/>
       <c r="N13" s="7" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="4">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>85</v>
@@ -2509,7 +2510,7 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="4">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>88</v>
@@ -2545,13 +2546,13 @@
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="6">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>13</v>
@@ -2578,18 +2579,18 @@
       <c r="L16" s="7"/>
       <c r="M16" s="7"/>
       <c r="N16" s="7" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="6">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>13</v>
@@ -2616,18 +2617,18 @@
       <c r="L17" s="7"/>
       <c r="M17" s="7"/>
       <c r="N17" s="7" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="6">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="B18" s="6" t="s">
+        <v>455</v>
+      </c>
+      <c r="C18" s="6" t="s">
         <v>456</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>457</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>13</v>
@@ -2654,12 +2655,12 @@
       <c r="L18" s="7"/>
       <c r="M18" s="7"/>
       <c r="N18" s="7" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="4">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>104</v>
@@ -2695,7 +2696,7 @@
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="8">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="B20" s="8" t="s">
         <v>106</v>
@@ -2733,7 +2734,7 @@
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="8">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="B21" s="8" t="s">
         <v>112</v>
@@ -2771,7 +2772,7 @@
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="8">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="B22" s="8" t="s">
         <v>115</v>
@@ -2809,7 +2810,7 @@
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="8">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="B23" s="8" t="s">
         <v>118</v>
@@ -2847,7 +2848,7 @@
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="8">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="B24" s="8" t="s">
         <v>121</v>
@@ -2885,7 +2886,7 @@
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="8">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="B25" s="8" t="s">
         <v>125</v>
@@ -2923,7 +2924,7 @@
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="8">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="B26" s="8" t="s">
         <v>128</v>
@@ -2961,7 +2962,7 @@
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="8">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="B27" s="8" t="s">
         <v>131</v>
@@ -2999,7 +3000,7 @@
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="8">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="B28" s="8" t="s">
         <v>135</v>
@@ -3037,7 +3038,7 @@
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="8">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="B29" s="8" t="s">
         <v>138</v>
@@ -3075,7 +3076,7 @@
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="8">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="B30" s="8" t="s">
         <v>141</v>
@@ -3113,7 +3114,7 @@
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="8">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="B31" s="8" t="s">
         <v>145</v>
@@ -3151,7 +3152,7 @@
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="8">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="B32" s="8" t="s">
         <v>148</v>
@@ -3189,7 +3190,7 @@
     </row>
     <row r="33" spans="1:14">
       <c r="A33" s="8">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="B33" s="8" t="s">
         <v>152</v>
@@ -3227,7 +3228,7 @@
     </row>
     <row r="34" spans="1:14">
       <c r="A34" s="8">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="B34" s="8" t="s">
         <v>155</v>
@@ -3265,7 +3266,7 @@
     </row>
     <row r="35" spans="1:14">
       <c r="A35" s="4">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>158</v>
@@ -3303,7 +3304,7 @@
     </row>
     <row r="36" spans="1:14">
       <c r="A36" s="8">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="B36" s="8" t="s">
         <v>162</v>
@@ -3341,7 +3342,7 @@
     </row>
     <row r="37" spans="1:14">
       <c r="A37" s="8">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="B37" s="8" t="s">
         <v>165</v>
@@ -3379,7 +3380,7 @@
     </row>
     <row r="38" spans="1:14">
       <c r="A38" s="8">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="B38" s="8" t="s">
         <v>168</v>
@@ -3417,7 +3418,7 @@
     </row>
     <row r="39" spans="1:14">
       <c r="A39" s="8">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="B39" s="8" t="s">
         <v>171</v>
@@ -3455,7 +3456,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="8">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="B40" s="8" t="s">
         <v>174</v>
@@ -3493,7 +3494,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="8">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="B41" s="8" t="s">
         <v>177</v>
@@ -3531,7 +3532,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="8">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="B42" s="8" t="s">
         <v>180</v>
@@ -3569,7 +3570,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="8">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="B43" s="8" t="s">
         <v>183</v>
@@ -3607,7 +3608,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="8">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="B44" s="8" t="s">
         <v>186</v>
@@ -3645,7 +3646,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="8">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="B45" s="8" t="s">
         <v>190</v>
@@ -3683,7 +3684,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="8">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="B46" s="8" t="s">
         <v>193</v>
@@ -3721,7 +3722,7 @@
     </row>
     <row r="47" spans="1:14">
       <c r="A47" s="4">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>196</v>
@@ -3757,7 +3758,7 @@
     </row>
     <row r="48" spans="1:14">
       <c r="A48" s="8">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="B48" s="8" t="s">
         <v>199</v>
@@ -3795,7 +3796,7 @@
     </row>
     <row r="49" spans="1:14">
       <c r="A49" s="4">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>202</v>
@@ -3831,7 +3832,7 @@
     </row>
     <row r="50" spans="1:14">
       <c r="A50" s="4">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="B50" s="4" t="s">
         <v>205</v>
@@ -3867,7 +3868,7 @@
     </row>
     <row r="51" spans="1:14">
       <c r="A51" s="4">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="B51" s="4" t="s">
         <v>208</v>
@@ -3903,7 +3904,7 @@
     </row>
     <row r="52" spans="1:14">
       <c r="A52" s="4">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="B52" s="4" t="s">
         <v>211</v>
@@ -3939,7 +3940,7 @@
     </row>
     <row r="53" spans="1:14">
       <c r="A53" s="8">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="B53" s="8" t="s">
         <v>214</v>
@@ -3977,7 +3978,7 @@
     </row>
     <row r="54" spans="1:14">
       <c r="A54" s="4">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="B54" s="4" t="s">
         <v>217</v>
@@ -4013,7 +4014,7 @@
     </row>
     <row r="55" spans="1:14">
       <c r="A55" s="4">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="B55" s="4" t="s">
         <v>220</v>
@@ -4049,7 +4050,7 @@
     </row>
     <row r="56" spans="1:14">
       <c r="A56" s="4">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="B56" s="4" t="s">
         <v>223</v>
@@ -4085,7 +4086,7 @@
     </row>
     <row r="57" spans="1:14">
       <c r="A57" s="4">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="B57" s="4" t="s">
         <v>226</v>
@@ -4121,7 +4122,7 @@
     </row>
     <row r="58" spans="1:14">
       <c r="A58" s="8">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="B58" s="8" t="s">
         <v>229</v>
@@ -4159,7 +4160,7 @@
     </row>
     <row r="59" spans="1:14">
       <c r="A59" s="4">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="B59" s="4" t="s">
         <v>232</v>
@@ -4195,7 +4196,7 @@
     </row>
     <row r="60" spans="1:14">
       <c r="A60" s="4">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="B60" s="4" t="s">
         <v>235</v>
@@ -4231,7 +4232,7 @@
     </row>
     <row r="61" spans="1:14">
       <c r="A61" s="4">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="B61" s="4" t="s">
         <v>239</v>
@@ -4267,7 +4268,7 @@
     </row>
     <row r="62" spans="1:14">
       <c r="A62" s="4">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="B62" s="4" t="s">
         <v>243</v>
@@ -4303,7 +4304,7 @@
     </row>
     <row r="63" spans="1:14">
       <c r="A63" s="4">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="B63" s="4" t="s">
         <v>247</v>
@@ -4339,7 +4340,7 @@
     </row>
     <row r="64" spans="1:14">
       <c r="A64" s="4">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="B64" s="4" t="s">
         <v>251</v>
@@ -4375,7 +4376,7 @@
     </row>
     <row r="65" spans="1:14">
       <c r="A65" s="4">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="B65" s="4" t="s">
         <v>254</v>
@@ -4413,7 +4414,7 @@
     </row>
     <row r="66" spans="1:14">
       <c r="A66" s="4">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="B66" s="4" t="s">
         <v>258</v>
@@ -4449,7 +4450,7 @@
     </row>
     <row r="67" spans="1:14">
       <c r="A67" s="4">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="B67" s="4" t="s">
         <v>262</v>
@@ -4485,7 +4486,7 @@
     </row>
     <row r="68" spans="1:14">
       <c r="A68" s="4">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="B68" s="4" t="s">
         <v>265</v>
@@ -4521,7 +4522,7 @@
     </row>
     <row r="69" spans="1:14">
       <c r="A69" s="4">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="B69" s="4" t="s">
         <v>268</v>
@@ -4559,7 +4560,7 @@
     </row>
     <row r="70" spans="1:14">
       <c r="A70" s="4">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="B70" s="4" t="s">
         <v>271</v>
@@ -4597,7 +4598,7 @@
     </row>
     <row r="71" spans="1:14">
       <c r="A71" s="4">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="B71" s="4" t="s">
         <v>274</v>
@@ -4635,7 +4636,7 @@
     </row>
     <row r="72" spans="1:14">
       <c r="A72" s="4">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="B72" s="4" t="s">
         <v>278</v>
@@ -4673,7 +4674,7 @@
     </row>
     <row r="73" spans="1:14">
       <c r="A73" s="4">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="B73" s="4" t="s">
         <v>282</v>
@@ -4711,7 +4712,7 @@
     </row>
     <row r="74" spans="1:14">
       <c r="A74" s="4">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="B74" s="4" t="s">
         <v>285</v>
@@ -4747,7 +4748,7 @@
     </row>
     <row r="75" spans="1:14">
       <c r="A75" s="4">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B75" s="4" t="s">
         <v>288</v>
@@ -4783,7 +4784,7 @@
     </row>
     <row r="76" spans="1:14">
       <c r="A76" s="4">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B76" s="4" t="s">
         <v>292</v>
@@ -4819,7 +4820,7 @@
     </row>
     <row r="77" spans="1:14">
       <c r="A77" s="4">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B77" s="4" t="s">
         <v>296</v>
@@ -4855,7 +4856,7 @@
     </row>
     <row r="78" spans="1:14">
       <c r="A78" s="4">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="B78" s="4" t="s">
         <v>299</v>
@@ -4891,7 +4892,7 @@
     </row>
     <row r="79" spans="1:14">
       <c r="A79" s="4">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="B79" s="4" t="s">
         <v>303</v>
@@ -4926,30 +4927,32 @@
       <c r="N79" s="5"/>
     </row>
     <row r="80" spans="1:14">
-      <c r="A80" s="4"/>
+      <c r="A80" s="4">
+        <v>79</v>
+      </c>
       <c r="B80" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="C80" s="4" t="s">
         <v>483</v>
       </c>
-      <c r="C80" s="4" t="s">
+      <c r="D80" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E80" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F80" s="4" t="s">
         <v>484</v>
       </c>
-      <c r="D80" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E80" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F80" s="4" t="s">
+      <c r="G80" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="H80" s="4">
+        <v>2</v>
+      </c>
+      <c r="I80" s="12" t="s">
         <v>485</v>
-      </c>
-      <c r="G80" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="H80" s="4">
-        <v>2</v>
-      </c>
-      <c r="I80" s="12" t="s">
-        <v>486</v>
       </c>
       <c r="J80" s="5" t="s">
         <v>23</v>
@@ -4963,7 +4966,7 @@
     </row>
     <row r="81" spans="1:14">
       <c r="A81" s="4">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="B81" s="4" t="s">
         <v>306</v>
@@ -4999,10 +5002,10 @@
     </row>
     <row r="82" spans="1:14">
       <c r="A82" s="4">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C82" s="4" t="s">
         <v>309</v>
@@ -5034,30 +5037,32 @@
       <c r="N82" s="5"/>
     </row>
     <row r="83" spans="1:14">
-      <c r="A83" s="4"/>
+      <c r="A83" s="4">
+        <v>82</v>
+      </c>
       <c r="B83" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="C83" s="4" t="s">
         <v>464</v>
       </c>
-      <c r="C83" s="4" t="s">
+      <c r="D83" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E83" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F83" s="4" t="s">
         <v>465</v>
       </c>
-      <c r="D83" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E83" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F83" s="4" t="s">
+      <c r="G83" s="12" t="s">
         <v>466</v>
-      </c>
-      <c r="G83" s="12" t="s">
-        <v>467</v>
       </c>
       <c r="H83" s="4">
         <v>4</v>
       </c>
       <c r="I83" s="12" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="J83" s="5" t="s">
         <v>23</v>
@@ -5071,7 +5076,7 @@
     </row>
     <row r="84" spans="1:14">
       <c r="A84" s="4">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="B84" s="4" t="s">
         <v>311</v>
@@ -5107,13 +5112,13 @@
     </row>
     <row r="85" spans="1:14">
       <c r="A85" s="8">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="B85" s="8" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C85" s="8" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="D85" s="8" t="s">
         <v>13</v>
@@ -5145,7 +5150,7 @@
     </row>
     <row r="86" spans="1:14">
       <c r="A86" s="4">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="B86" s="4" t="s">
         <v>317</v>
@@ -5181,7 +5186,7 @@
     </row>
     <row r="87" spans="1:14">
       <c r="A87" s="4">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="B87" s="4" t="s">
         <v>320</v>
@@ -5217,7 +5222,7 @@
     </row>
     <row r="88" spans="1:14">
       <c r="A88" s="4">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="B88" s="4" t="s">
         <v>323</v>
@@ -5253,7 +5258,7 @@
     </row>
     <row r="89" spans="1:14">
       <c r="A89" s="4">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="B89" s="4" t="s">
         <v>327</v>
@@ -5289,7 +5294,7 @@
     </row>
     <row r="90" spans="1:14">
       <c r="A90" s="4">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="B90" s="4" t="s">
         <v>330</v>
@@ -5325,7 +5330,7 @@
     </row>
     <row r="91" spans="1:14">
       <c r="A91" s="8">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="B91" s="8" t="s">
         <v>333</v>
@@ -5363,7 +5368,7 @@
     </row>
     <row r="92" spans="1:14">
       <c r="A92" s="4">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="B92" s="4" t="s">
         <v>336</v>
@@ -5399,7 +5404,7 @@
     </row>
     <row r="93" spans="1:14">
       <c r="A93" s="4">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="B93" s="4" t="s">
         <v>339</v>
@@ -5478,7 +5483,7 @@
         <v>44</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>42</v>
@@ -5490,7 +5495,7 @@
         <v>43</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="26">
@@ -5498,7 +5503,7 @@
         <v>44</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>47</v>
@@ -5510,7 +5515,7 @@
         <v>48</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="26">
@@ -5518,7 +5523,7 @@
         <v>44</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>50</v>
@@ -5530,7 +5535,7 @@
         <v>51</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="26">
@@ -5538,7 +5543,7 @@
         <v>44</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>53</v>
@@ -5550,7 +5555,7 @@
         <v>54</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="26">
@@ -5558,7 +5563,7 @@
         <v>44</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>56</v>
@@ -5570,7 +5575,7 @@
         <v>57</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="26">
@@ -5578,7 +5583,7 @@
         <v>44</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>59</v>
@@ -5590,7 +5595,7 @@
         <v>60</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="26">
@@ -5598,7 +5603,7 @@
         <v>44</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>62</v>
@@ -5607,10 +5612,10 @@
         <v>66</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="26">
@@ -5618,7 +5623,7 @@
         <v>44</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>63</v>
@@ -5627,10 +5632,10 @@
         <v>77</v>
       </c>
       <c r="E9" s="7" t="s">
+        <v>438</v>
+      </c>
+      <c r="F9" s="7" t="s">
         <v>439</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>440</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="26">
@@ -5638,7 +5643,7 @@
         <v>44</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>64</v>
@@ -5650,7 +5655,7 @@
         <v>65</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -5658,7 +5663,7 @@
         <v>69</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>67</v>
@@ -5670,7 +5675,7 @@
         <v>68</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -5678,7 +5683,7 @@
         <v>69</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>72</v>
@@ -5690,7 +5695,7 @@
         <v>73</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -5698,7 +5703,7 @@
         <v>69</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>75</v>
@@ -5710,7 +5715,7 @@
         <v>76</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -5718,7 +5723,7 @@
         <v>80</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>78</v>
@@ -5730,7 +5735,7 @@
         <v>79</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -5738,7 +5743,7 @@
         <v>80</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>81</v>
@@ -5750,7 +5755,7 @@
         <v>82</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -5758,7 +5763,7 @@
         <v>80</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>83</v>
@@ -5770,7 +5775,7 @@
         <v>84</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5778,7 +5783,7 @@
         <v>77</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>91</v>
@@ -5790,7 +5795,7 @@
         <v>92</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -5798,7 +5803,7 @@
         <v>77</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>93</v>
@@ -5810,7 +5815,7 @@
         <v>94</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -5818,7 +5823,7 @@
         <v>97</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>95</v>
@@ -5830,7 +5835,7 @@
         <v>96</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -5838,7 +5843,7 @@
         <v>97</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>98</v>
@@ -5850,7 +5855,7 @@
         <v>99</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -5858,7 +5863,7 @@
         <v>101</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>100</v>
@@ -5867,10 +5872,10 @@
         <v>45</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -5878,7 +5883,7 @@
         <v>101</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>102</v>
@@ -5887,10 +5892,10 @@
         <v>49</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -5898,7 +5903,7 @@
         <v>101</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>103</v>
@@ -5907,10 +5912,10 @@
         <v>52</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -7075,13 +7080,13 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82" s="8" t="s">
+        <v>468</v>
+      </c>
+      <c r="B82" s="8" t="s">
         <v>469</v>
       </c>
-      <c r="B82" s="8" t="s">
-        <v>470</v>
-      </c>
       <c r="C82" s="8" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D82" s="8" t="s">
         <v>109</v>
@@ -7095,13 +7100,13 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" s="8" t="s">
+        <v>468</v>
+      </c>
+      <c r="B83" s="8" t="s">
         <v>469</v>
       </c>
-      <c r="B83" s="8" t="s">
-        <v>470</v>
-      </c>
       <c r="C83" s="8" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D83" s="8" t="s">
         <v>316</v>
@@ -7182,13 +7187,13 @@
         <v>418</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>419</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>420</v>
@@ -7202,7 +7207,7 @@
         <v>421</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C2" s="3">
         <v>0</v>
@@ -7211,7 +7216,7 @@
         <v>16</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>422</v>
@@ -7225,7 +7230,7 @@
         <v>421</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C3" s="3">
         <f>C2+D2</f>
@@ -7235,7 +7240,7 @@
         <v>16</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>422</v>
@@ -7273,7 +7278,7 @@
         <v>421</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>427</v>
+        <v>486</v>
       </c>
       <c r="C5" s="3">
         <f t="shared" si="0"/>
@@ -7283,13 +7288,13 @@
         <v>14</v>
       </c>
       <c r="E5" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>428</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="G5" s="3" t="s">
         <v>429</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -7297,7 +7302,7 @@
         <v>421</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C6" s="3">
         <f t="shared" si="0"/>
@@ -7308,18 +7313,18 @@
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>432</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="3" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C7" s="3">
         <f t="shared" si="0"/>
@@ -7334,10 +7339,10 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>435</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>436</v>
       </c>
       <c r="C8" s="3">
         <f t="shared" si="0"/>
@@ -7349,7 +7354,7 @@
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="3" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
   </sheetData>
